--- a/backend/backups/category2_cleaning_home_FINAL.xlsx
+++ b/backend/backups/category2_cleaning_home_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,65 +425,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
@@ -512,817 +493,897 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deep Cleaning Service Variation 1</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Deep Cleaning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deep Cleaning</t>
+          <t>Balcony Washing &amp; Window Track Cleaning</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Pressure washing balcony floor, wiping glass railings, and vacuuming dirt from sliding window tracks.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Complete Deep Cleaning Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Balcony Washing &amp; Window Track Cleaning procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Deep Cleaning Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Deep Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Deep Cleaning Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Deep Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Deep Cleaning Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Deep Cleaning Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Balcony Washing &amp; Window Track Cleaning procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.569736+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.569736+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Balcony Washing &amp; Window Track Cleaning take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>58ebfd65-2645-4370-b241-aca8a67e6a67</t>
+          <t>264904c6-aad9-4106-ac12-d8a108b29bba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deep Cleaning Service Variation 2</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Deep Cleaning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deep Cleaning</t>
+          <t>Bathroom Tile Scrubbing &amp; Descaling Wash</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Acid-free hard water stain removal from floor/wall tiles, glass shower partitions, taps, and toilet bowls.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Complete Deep Cleaning Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Bathroom Tile Scrubbing &amp; Descaling Wash procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Deep Cleaning Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Deep Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Deep Cleaning Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Deep Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Deep Cleaning Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Deep Cleaning Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Bathroom Tile Scrubbing &amp; Descaling Wash procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.574939+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.574939+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Bathroom Tile Scrubbing &amp; Descaling Wash take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f40e6092-ddcd-4d8e-aaf1-be9fdbacbc0e</t>
+          <t>42e0784e-4fef-497f-a2cc-415631f57b6c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deep Cleaning Service Variation 3</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Deep Cleaning</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deep Cleaning</t>
+          <t>Floor Machine Scrubbing &amp; Buffing</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Single-disc rotary floor scrubbing machine treatment for marble, granite, or vitrified tile shine.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Complete Deep Cleaning Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Floor Machine Scrubbing &amp; Buffing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Deep Cleaning Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Deep Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Deep Cleaning Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Deep Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Deep Cleaning Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Deep Cleaning Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Floor Machine Scrubbing &amp; Buffing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.579087+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.579087+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Floor Machine Scrubbing &amp; Buffing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>c7529e16-f7f1-4785-bbf7-1e572aeaaaf0</t>
+          <t>0425f57a-ce8d-457f-b1d2-c387ce4daa56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deep Cleaning Service Variation 4</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Deep Cleaning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deep Cleaning</t>
+          <t>Full Apartment Deep Cleaning (1/2 BHK)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>999</v>
+        <v>2999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Thorough top-to-bottom scrub of entire home including ceiling fans, window sills, doors, floors, and sanitization.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Complete Deep Cleaning Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Full Apartment Deep Cleaning (1/2 BHK) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Deep Cleaning Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Deep Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Deep Cleaning Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Deep Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Deep Cleaning Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Deep Cleaning Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Full Apartment Deep Cleaning (1/2 BHK) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.581934+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.581934+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does Full Apartment Deep Cleaning (1/2 BHK) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5ace55fc-4278-4f14-b54f-4a695af2bb7c</t>
+          <t>0594444a-63a4-4543-aa9a-db671cb4b269</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deep Cleaning Service Variation 5</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Deep Cleaning</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deep Cleaning</t>
+          <t>Kitchen Oil Degreasing &amp; Cabinet Deep Clean</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>999</v>
+        <v>1299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Heavy-duty chemical degreasing of grease-laden kitchen tiles, cabinet interiors/exteriors, and exhaust fans.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Complete Deep Cleaning Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Kitchen Oil Degreasing &amp; Cabinet Deep Clean procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Deep Cleaning Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Deep Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Deep Cleaning Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Deep Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Deep Cleaning Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Deep Cleaning Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Kitchen Oil Degreasing &amp; Cabinet Deep Clean procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.584644+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.584644+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Kitchen Oil Degreasing &amp; Cabinet Deep Clean take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>58b3d78f-5bbd-4d31-b1e4-c59555344a73</t>
+          <t>2926232b-ec38-4f63-96e5-fc359856ceae</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deep Cleaning Service Variation 6</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Deep Cleaning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deep Cleaning</t>
+          <t>Move-In / Move-Out Sanitize Deep Clean</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>999</v>
+        <v>3499</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Comprehensive disinfection and deep cleaning for vacant houses prior to moving in or handing over to landlord.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Complete Deep Cleaning Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Move-In / Move-Out Sanitize Deep Clean procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Deep Cleaning Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Deep Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Deep Cleaning Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Deep Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Deep Cleaning Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Deep Cleaning Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Move-In / Move-Out Sanitize Deep Clean procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.588569+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.588569+00:00</t>
+          <t>[{'answer': 'The session typically takes around 240 minutes.', 'question': 'How long does Move-In / Move-Out Sanitize Deep Clean take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42e0784e-4fef-497f-a2cc-415631f57b6c</t>
+          <t>3f3e2d4d-153a-4367-921a-7d6005dd532d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deep Cleaning Service Variation 7</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Deep Cleaning</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deep Cleaning</t>
+          <t>Terrace &amp; Roof High-Pressure Wash</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>999</v>
+        <v>1599</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Industrial jet washer cleaning of rooftop tiles, rainwater drains, and moss buildup removal.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Complete Deep Cleaning Service Variation 7 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Terrace &amp; Roof High-Pressure Wash procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Deep Cleaning Service Variation 7 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Deep Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Deep Cleaning Service Variation 7 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Deep Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Deep Cleaning Service Variation 7 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Deep Cleaning Service Variation 7 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Terrace &amp; Roof High-Pressure Wash procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.591249+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.591249+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Terrace &amp; Roof High-Pressure Wash take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6efaf71d-0b05-4cb0-94dc-a624f7c103a0</t>
+          <t>58b3d78f-5bbd-4d31-b1e4-c59555344a73</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 1</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>1 BHK Express Deep Cleaning</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>999</v>
+        <v>1999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Complete cleaning of 1 hall, 1 bedroom, 1 kitchen, and 1 bathroom with eco-friendly cleaning agents.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional 1 BHK Express Deep Cleaning procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 1 BHK Express Deep Cleaning procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.594537+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.594537+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does 1 BHK Express Deep Cleaning take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cdd0be50-0dba-4241-bb94-06edf5d735dd</t>
+          <t>58ebfd65-2645-4370-b241-aca8a67e6a67</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 2</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>2 BHK Standard Full Home Cleaning</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>999</v>
+        <v>2799</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Detailed deep cleaning service for 2 BHK flats covering all rooms, fixtures, and floor scrubbing.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional 2 BHK Standard Full Home Cleaning procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 2 BHK Standard Full Home Cleaning procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.597159+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.597159+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does 2 BHK Standard Full Home Cleaning take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>adc6b8c0-dcad-4a57-b1a3-f20be2d2e05b</t>
+          <t>5ace55fc-4278-4f14-b54f-4a695af2bb7c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 3</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>3 BHK Premium Full Home Cleaning</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>999</v>
+        <v>3699</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>4-member cleaner team deep cleaning 3 bedrooms, hall, kitchen, balconies, and 3 bathrooms.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional 3 BHK Premium Full Home Cleaning procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 3 BHK Premium Full Home Cleaning procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.600049+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.600049+00:00</t>
+          <t>[{'answer': 'The session typically takes around 240 minutes.', 'question': 'How long does 3 BHK Premium Full Home Cleaning take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>c8bfc80e-aa4d-48a9-8d78-41a62ff587cb</t>
+          <t>6b33aec0-8146-413b-b0d3-de90b3d5d137</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 4</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>4 BHK / Villa Luxury Deep Cleaning</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>999</v>
+        <v>4999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Full day deep cleaning for large villas, independent houses, or 4 BHK duplex apartments.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional 4 BHK / Villa Luxury Deep Cleaning procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 4 BHK / Villa Luxury Deep Cleaning procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.603788+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.603788+00:00</t>
+          <t>[{'answer': 'The session typically takes around 300 minutes.', 'question': 'How long does 4 BHK / Villa Luxury Deep Cleaning take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e452fe98-b0b0-485a-ba63-7deb57ca7f89</t>
+          <t>7b455532-df98-4d31-8e28-b73988cb1607</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 5</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>Dining Area Scrubbing &amp; Sanitization</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Deep cleaning dining table, chair wipe down, floor stain removal, and chandelier dusting.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Dining Area Scrubbing &amp; Sanitization procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dining Area Scrubbing &amp; Sanitization procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.606421+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.606421+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Dining Area Scrubbing &amp; Sanitization take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7b455532-df98-4d31-8e28-b73988cb1607</t>
+          <t>6efaf71d-0b05-4cb0-94dc-a624f7c103a0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 6</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>Living Room Furniture Polish &amp; Clean</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>TV unit dusting, sofa vacuuming, glass center table cleaning, and floor scrubbing in hall.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Living Room Furniture Polish &amp; Clean procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Living Room Furniture Polish &amp; Clean procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.608991+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.608991+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Living Room Furniture Polish &amp; Clean take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8a8c6e5c-1b99-43f2-9606-5fa63d9e4a49</t>
+          <t>6d6239bc-2c85-4e75-809d-5a9dfb5418b0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 7</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>Single Bedroom Deep Dust &amp; Vacuum</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Cobweb removal, wardrobe top dusting, mattress vacuuming, and floor mopping for 1 bedroom.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 7 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Single Bedroom Deep Dust &amp; Vacuum procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 7 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 7 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 7 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 7 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Single Bedroom Deep Dust &amp; Vacuum procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.611049+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.611049+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Single Bedroom Deep Dust &amp; Vacuum take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fa2970d3-b25c-4521-b61b-efeb396dadac</t>
+          <t>8a8c6e5c-1b99-43f2-9606-5fa63d9e4a49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning Service Variation 8</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Full Home / By Room Cleaning</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Full Home / By Room Cleaning</t>
+          <t>Store Room &amp; Attic Declutter Cleaning</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Organizing, dusting, cobweb removal, and floor wash for storage rooms and lofts.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Complete Full Home / By Room Cleaning Service Variation 8 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Store Room &amp; Attic Declutter Cleaning procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Full Home / By Room Cleaning Service Variation 8 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Full Home / By Room Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Full Home / By Room Cleaning Service Variation 8 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Full Home / By Room Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Full Home / By Room Cleaning Service Variation 8 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Full Home / By Room Cleaning Service Variation 8 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Store Room &amp; Attic Declutter Cleaning procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.613363+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.613363+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Store Room &amp; Attic Declutter Cleaning take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f7804888-0442-4dff-b91f-e543ea8182ae</t>
+          <t>adc6b8c0-dcad-4a57-b1a3-f20be2d2e05b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning Service Variation 1</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Kitchen &amp; Bathroom Cleaning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning</t>
+          <t>Dual Bathroom Scrubbing &amp; Tile Polish</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>999</v>
+        <v>1299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Value combo package deep scrubbing 2 bathrooms including washbasin, mirror, and toilet disinfections.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Complete Kitchen &amp; Bathroom Cleaning Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Dual Bathroom Scrubbing &amp; Tile Polish procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Kitchen &amp; Bathroom Cleaning Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Kitchen &amp; Bathroom Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Kitchen &amp; Bathroom Cleaning Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Kitchen &amp; Bathroom Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Kitchen &amp; Bathroom Cleaning Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Kitchen &amp; Bathroom Cleaning Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Dual Bathroom Scrubbing &amp; Tile Polish procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.615513+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.615513+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Dual Bathroom Scrubbing &amp; Tile Polish take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>264904c6-aad9-4106-ac12-d8a108b29bba</t>
+          <t>990f4a13-a171-43cc-b364-1e1022122d8d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning Service Variation 2</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Kitchen &amp; Bathroom Cleaning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning</t>
+          <t>Kitchen Cabinet &amp; Appliance Exterior Wash</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1330,699 +1391,769 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Wiping inside empty cabinets, degreasing fridge exterior, microwave exterior, and countertop scrub.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Complete Kitchen &amp; Bathroom Cleaning Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Kitchen Cabinet &amp; Appliance Exterior Wash procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Kitchen &amp; Bathroom Cleaning Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Kitchen &amp; Bathroom Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Kitchen &amp; Bathroom Cleaning Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Kitchen &amp; Bathroom Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Kitchen &amp; Bathroom Cleaning Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Kitchen &amp; Bathroom Cleaning Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Kitchen Cabinet &amp; Appliance Exterior Wash procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.618525+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.618525+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Kitchen Cabinet &amp; Appliance Exterior Wash take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cedcf4c4-a0c8-460c-9aa3-dd839f66e80f</t>
+          <t>9a614042-e18d-4ab9-886a-0b07c93ef01a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning Service Variation 3</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Kitchen &amp; Bathroom Cleaning</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning</t>
+          <t>Kitchen Chimney &amp; Hob Deep Degreasing</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Dismantling chimney mesh filters, chemical degreasing bath, and gas stove burner cleaning.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Complete Kitchen &amp; Bathroom Cleaning Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Kitchen Chimney &amp; Hob Deep Degreasing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Kitchen &amp; Bathroom Cleaning Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Kitchen &amp; Bathroom Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Kitchen &amp; Bathroom Cleaning Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Kitchen &amp; Bathroom Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Kitchen &amp; Bathroom Cleaning Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Kitchen &amp; Bathroom Cleaning Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Kitchen Chimney &amp; Hob Deep Degreasing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.621652+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.621652+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Kitchen Chimney &amp; Hob Deep Degreasing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>990f4a13-a171-43cc-b364-1e1022122d8d</t>
+          <t>c4aef5dc-1115-4e65-a8c0-30f7ead61994</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning Service Variation 4</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Kitchen &amp; Bathroom Cleaning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning</t>
+          <t>Kitchen Countertop &amp; Wall Tile Steam Clean</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>High-temperature steam spray dissolving oil drops on backsplashes and grout joints.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Complete Kitchen &amp; Bathroom Cleaning Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Kitchen Countertop &amp; Wall Tile Steam Clean procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Kitchen &amp; Bathroom Cleaning Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Kitchen &amp; Bathroom Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Kitchen &amp; Bathroom Cleaning Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Kitchen &amp; Bathroom Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Kitchen &amp; Bathroom Cleaning Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Kitchen &amp; Bathroom Cleaning Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Kitchen Countertop &amp; Wall Tile Steam Clean procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.624473+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.624473+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Kitchen Countertop &amp; Wall Tile Steam Clean take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6b33aec0-8146-413b-b0d3-de90b3d5d137</t>
+          <t>bffc5df7-1c34-44fb-80dd-84fb1d9be2c1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning Service Variation 5</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Kitchen &amp; Bathroom Cleaning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kitchen &amp; Bathroom Cleaning</t>
+          <t>Sink Drain Unclogging &amp; Anti-Bacterial Wash</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>999</v>
+        <v>399</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Clearing slow kitchen sink drains, removing sludge, and flushing with odor-killing enzyme gel.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Complete Kitchen &amp; Bathroom Cleaning Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Sink Drain Unclogging &amp; Anti-Bacterial Wash procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Kitchen &amp; Bathroom Cleaning Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Kitchen &amp; Bathroom Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Kitchen &amp; Bathroom Cleaning Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Kitchen &amp; Bathroom Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Kitchen &amp; Bathroom Cleaning Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Kitchen &amp; Bathroom Cleaning Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Sink Drain Unclogging &amp; Anti-Bacterial Wash procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.626816+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.626816+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Sink Drain Unclogging &amp; Anti-Bacterial Wash take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fed5e15c-ad8c-4dcd-9fc5-bfdaad37d7a8</t>
+          <t>cdd0be50-0dba-4241-bb94-06edf5d735dd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pest Control Service Variation 1</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Pest Control</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Anti-Termite Soil Drilling &amp; Barrier Injection</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>999</v>
+        <v>2499</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Drilling holes along wall skirts and injecting anti-termite chemical to protect wooden furniture with 2-year warranty.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Complete Pest Control Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Anti-Termite Soil Drilling &amp; Barrier Injection procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pest Control Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pest Control experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pest Control Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pest Control tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pest Control Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pest Control Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Anti-Termite Soil Drilling &amp; Barrier Injection procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.629720+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.629720+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Anti-Termite Soil Drilling &amp; Barrier Injection take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0594444a-63a4-4543-aa9a-db671cb4b269</t>
+          <t>d3677ffb-f3e5-4454-86b3-5a7b6d9fdad1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pest Control Service Variation 2</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Pest Control</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Ant &amp; Silverfish Perimeter Spray</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Odorless liquid barrier spray along sugar ant trails, bookshelves, and bathroom baseboards.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Complete Pest Control Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Ant &amp; Silverfish Perimeter Spray procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pest Control Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pest Control experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pest Control Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pest Control tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pest Control Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pest Control Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Ant &amp; Silverfish Perimeter Spray procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.632451+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.632451+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Ant &amp; Silverfish Perimeter Spray take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3f3e2d4d-153a-4367-921a-7d6005dd532d</t>
+          <t>c8bfc80e-aa4d-48a9-8d78-41a62ff587cb</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pest Control Service Variation 3</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Pest Control</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Bed Bug Thermal &amp; Chemical Treatment</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>999</v>
+        <v>1499</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>2-visit spray treatment targeting mattress seams, bed frames, and wall cracks for complete bed bug eradication.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Complete Pest Control Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Bed Bug Thermal &amp; Chemical Treatment procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pest Control Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pest Control experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pest Control Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pest Control tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pest Control Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pest Control Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Bed Bug Thermal &amp; Chemical Treatment procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.635650+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.635650+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Bed Bug Thermal &amp; Chemical Treatment take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ed433b58-b961-4023-9192-a7d45601daa2</t>
+          <t>c7529e16-f7f1-4785-bbf7-1e572aeaaaf0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pest Control Service Variation 4</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Pest Control</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Cockroach Herbal Gel Pest Control</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Odorless herbal gel baiting in kitchen cabinets and drain spray exterminating German cockroaches.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Complete Pest Control Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Cockroach Herbal Gel Pest Control procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pest Control Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pest Control experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pest Control Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pest Control tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pest Control Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pest Control Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Cockroach Herbal Gel Pest Control procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.639474+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.639474+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Cockroach Herbal Gel Pest Control take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9a614042-e18d-4ab9-886a-0b07c93ef01a</t>
+          <t>cedcf4c4-a0c8-460c-9aa3-dd839f66e80f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pest Control Service Variation 5</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Pest Control</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Mosquito &amp; Fly Thermal Fogging</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Synthetic pyrethroid fogging for garden, balcony, and living areas suppressing adult mosquitoes.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Complete Pest Control Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Mosquito &amp; Fly Thermal Fogging procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pest Control Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pest Control experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pest Control Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pest Control tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pest Control Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pest Control Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Mosquito &amp; Fly Thermal Fogging procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.641898+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.641898+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Mosquito &amp; Fly Thermal Fogging take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>d3677ffb-f3e5-4454-86b3-5a7b6d9fdad1</t>
+          <t>d42758ef-14dd-4683-a944-80cc0c488fcf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pest Control Service Variation 6</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Pest Control</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Rodent Trapping &amp; Entry Sealing Service</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Placement of glue pads, snap traps, and sealing open pipe gaps to keep rats and mice out.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Complete Pest Control Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Rodent Trapping &amp; Entry Sealing Service procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pest Control Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pest Control experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pest Control Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pest Control tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pest Control Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pest Control Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Rodent Trapping &amp; Entry Sealing Service procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.644601+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.644601+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Rodent Trapping &amp; Entry Sealing Service take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>d42758ef-14dd-4683-a944-80cc0c488fcf</t>
+          <t>e452fe98-b0b0-485a-ba63-7deb57ca7f89</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning Service Variation 1</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Sofa &amp; Furniture Cleaning</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning</t>
+          <t>5-Seater Fabric Sofa Shampooing &amp; Extraction</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Injection-extraction foam machine washing removing deep stains, sweat odors, and dust mites from sofa.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Complete Sofa &amp; Furniture Cleaning Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional 5-Seater Fabric Sofa Shampooing &amp; Extraction procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Sofa &amp; Furniture Cleaning Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Sofa &amp; Furniture Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Sofa &amp; Furniture Cleaning Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Sofa &amp; Furniture Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Sofa &amp; Furniture Cleaning Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Sofa &amp; Furniture Cleaning Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 5-Seater Fabric Sofa Shampooing &amp; Extraction procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.646807+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.646807+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does 5-Seater Fabric Sofa Shampooing &amp; Extraction take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0425f57a-ce8d-457f-b1d2-c387ce4daa56</t>
+          <t>f40e6092-ddcd-4d8e-aaf1-be9fdbacbc0e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning Service Variation 2</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Sofa &amp; Furniture Cleaning</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning</t>
+          <t>6-Seater Dining Chair Upholstery Foam Wash</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Shampooing cushion seats of 6 dining chairs and polishing wooden/metal chair legs.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["Complete Sofa &amp; Furniture Cleaning Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional 6-Seater Dining Chair Upholstery Foam Wash procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Sofa &amp; Furniture Cleaning Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Sofa &amp; Furniture Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Sofa &amp; Furniture Cleaning Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Sofa &amp; Furniture Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Sofa &amp; Furniture Cleaning Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Sofa &amp; Furniture Cleaning Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 6-Seater Dining Chair Upholstery Foam Wash procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.649516+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.649516+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does 6-Seater Dining Chair Upholstery Foam Wash take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2926232b-ec38-4f63-96e5-fc359856ceae</t>
+          <t>fa2970d3-b25c-4521-b61b-efeb396dadac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning Service Variation 3</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Sofa &amp; Furniture Cleaning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning</t>
+          <t>Carpet High-Extraction Deep Wash</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Rug and living room carpet shampooing lifting tea/coffee spots and reviving carpet pile texture.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["Complete Sofa &amp; Furniture Cleaning Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Carpet High-Extraction Deep Wash procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Sofa &amp; Furniture Cleaning Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Sofa &amp; Furniture Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Sofa &amp; Furniture Cleaning Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Sofa &amp; Furniture Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Sofa &amp; Furniture Cleaning Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Sofa &amp; Furniture Cleaning Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Carpet High-Extraction Deep Wash procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.653614+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.653614+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Carpet High-Extraction Deep Wash take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>c4aef5dc-1115-4e65-a8c0-30f7ead61994</t>
+          <t>f7804888-0442-4dff-b91f-e543ea8182ae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning Service Variation 4</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Sofa &amp; Furniture Cleaning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning</t>
+          <t>King Size Mattress Deep Steam Sanitization</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>High-powered UV vacuuming and hot steam treatment sanitizing mattress from dead skin &amp; allergens.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["Complete Sofa &amp; Furniture Cleaning Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional King Size Mattress Deep Steam Sanitization procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Sofa &amp; Furniture Cleaning Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Sofa &amp; Furniture Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Sofa &amp; Furniture Cleaning Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Sofa &amp; Furniture Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Sofa &amp; Furniture Cleaning Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Sofa &amp; Furniture Cleaning Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete King Size Mattress Deep Steam Sanitization procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.656883+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.656883+00:00</t>
+          <t>[{'answer': 'The session typically takes around 50 minutes.', 'question': 'How long does King Size Mattress Deep Steam Sanitization take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bffc5df7-1c34-44fb-80dd-84fb1d9be2c1</t>
+          <t>ed433b58-b961-4023-9192-a7d45601daa2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning Service Variation 5</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Sofa &amp; Furniture Cleaning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning</t>
+          <t>Leather Sofa Conditioning &amp; Cream Polish</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2030,77 +2161,87 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized leather cleaner wiping dirt followed by rich moisturizer cream to prevent leather cracking.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>["Complete Sofa &amp; Furniture Cleaning Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Leather Sofa Conditioning &amp; Cream Polish procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Sofa &amp; Furniture Cleaning Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Sofa &amp; Furniture Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Sofa &amp; Furniture Cleaning Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Sofa &amp; Furniture Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Sofa &amp; Furniture Cleaning Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Sofa &amp; Furniture Cleaning Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Leather Sofa Conditioning &amp; Cream Polish procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.659194+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.659194+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Leather Sofa Conditioning &amp; Cream Polish take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6d6239bc-2c85-4e75-809d-5a9dfb5418b0</t>
+          <t>fed5e15c-ad8c-4dcd-9fc5-bfdaad37d7a8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning Service Variation 6</t>
+          <t>2. Cleaning &amp; Pest Control</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2. Cleaning &amp; Pest Control</t>
+          <t>Sofa &amp; Furniture Cleaning</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sofa &amp; Furniture Cleaning</t>
+          <t>Recliner Chair Spot &amp; Stain Scrub</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Targeted stain removal scrub and fabric wash for single electronic or manual recliner chairs.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>["Complete Sofa &amp; Furniture Cleaning Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Recliner Chair Spot &amp; Stain Scrub procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Sofa &amp; Furniture Cleaning Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Sofa &amp; Furniture Cleaning experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Sofa &amp; Furniture Cleaning Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Sofa &amp; Furniture Cleaning tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Sofa &amp; Furniture Cleaning Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Sofa &amp; Furniture Cleaning Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Recliner Chair Spot &amp; Stain Scrub procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.661377+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-05T14:21:17.661377+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Recliner Chair Spot &amp; Stain Scrub take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
